--- a/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109535</t>
+          <t>108945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142688</t>
+          <t>143390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>98026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125581</t>
+          <t>125846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213272</t>
+          <t>216249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258614</t>
+          <t>262390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139080</t>
+          <t>138378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172233</t>
+          <t>172823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80770</t>
+          <t>80505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108748</t>
+          <t>108325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229505</t>
+          <t>225729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274847</t>
+          <t>271870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79534</t>
+          <t>79936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109840</t>
+          <t>111103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131051</t>
+          <t>131347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160070</t>
+          <t>159436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219826</t>
+          <t>219869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>261028</t>
+          <t>260730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86678</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116984</t>
+          <t>116582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63418</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>92141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158978</t>
+          <t>159276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200180</t>
+          <t>200137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116784</t>
+          <t>116500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>150847</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>59368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82246</t>
+          <t>82282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183930</t>
+          <t>181625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225577</t>
+          <t>225691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>186875</t>
+          <t>188402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222465</t>
+          <t>222749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>43825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66565</t>
+          <t>66739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239779</t>
+          <t>239665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281426</t>
+          <t>283731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238562</t>
+          <t>243145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>293280</t>
+          <t>294418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241791</t>
+          <t>244615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>285554</t>
+          <t>287352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>500338</t>
+          <t>497461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568826</t>
+          <t>564099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483339</t>
+          <t>482201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>538057</t>
+          <t>533474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184437</t>
+          <t>182639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228200</t>
+          <t>225376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677784</t>
+          <t>682511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746272</t>
+          <t>749149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>83095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177454</t>
+          <t>177166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219987</t>
+          <t>218599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244604</t>
+          <t>243841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296555</t>
+          <t>294026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122144</t>
+          <t>124104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150637</t>
+          <t>151215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185744</t>
+          <t>187132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>228277</t>
+          <t>228565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316376</t>
+          <t>318905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368327</t>
+          <t>369090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240094</t>
+          <t>240561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>291412</t>
+          <t>293200</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>253193</t>
+          <t>252819</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>310921</t>
+          <t>309824</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81933</t>
+          <t>83092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97247</t>
+          <t>97284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>577209</t>
+          <t>575421</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>628527</t>
+          <t>628060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>664543</t>
+          <t>665640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>722271</t>
+          <t>722645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>659868</t>
+          <t>663650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>744868</t>
+          <t>745626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1010367</t>
+          <t>1012598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1111121</t>
+          <t>1108999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1700276</t>
+          <t>1701223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1828759</t>
+          <t>1826901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1163328</t>
+          <t>1162570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1248328</t>
+          <t>1244546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1189168</t>
+          <t>1191290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1289922</t>
+          <t>1287691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2379727</t>
+          <t>2381585</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2508210</t>
+          <t>2507263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144306</t>
+          <t>145246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176972</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151403</t>
+          <t>151087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177866</t>
+          <t>176539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306685</t>
+          <t>304302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>347135</t>
+          <t>345108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78249</t>
+          <t>77156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110915</t>
+          <t>109975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>30250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>55702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114874</t>
+          <t>116901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155324</t>
+          <t>157707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139654</t>
+          <t>141402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175332</t>
+          <t>177729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186110</t>
+          <t>185038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209747</t>
+          <t>209007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>334172</t>
+          <t>334342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379182</t>
+          <t>380889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94951</t>
+          <t>92554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130629</t>
+          <t>128881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>28153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51050</t>
+          <t>52122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128261</t>
+          <t>126554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173271</t>
+          <t>173101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181648</t>
+          <t>181046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223570</t>
+          <t>223247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95807</t>
+          <t>96010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120610</t>
+          <t>121377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284896</t>
+          <t>285940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>335935</t>
+          <t>336377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185363</t>
+          <t>185686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227285</t>
+          <t>227887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62317</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87120</t>
+          <t>86917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255925</t>
+          <t>255483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306964</t>
+          <t>305920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339481</t>
+          <t>341149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397644</t>
+          <t>395780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>387984</t>
+          <t>384482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>426187</t>
+          <t>422799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>738720</t>
+          <t>736295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>810856</t>
+          <t>809740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382074</t>
+          <t>383938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440237</t>
+          <t>438569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95516</t>
+          <t>98904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133719</t>
+          <t>137221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>490565</t>
+          <t>491681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>562701</t>
+          <t>565126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129530</t>
+          <t>127939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165760</t>
+          <t>162768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>335449</t>
+          <t>338877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385665</t>
+          <t>385903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>477368</t>
+          <t>476419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>536293</t>
+          <t>539260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154591</t>
+          <t>157583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190821</t>
+          <t>192412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200279</t>
+          <t>200041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250495</t>
+          <t>247067</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370002</t>
+          <t>367035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428927</t>
+          <t>429876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>277243</t>
+          <t>277298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>333762</t>
+          <t>333175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>293573</t>
+          <t>293543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>350623</t>
+          <t>352619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76470</t>
+          <t>76870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92692</t>
+          <t>92038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>441439</t>
+          <t>442026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>497958</t>
+          <t>497903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527399</t>
+          <t>525403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584449</t>
+          <t>584479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1006826</t>
+          <t>1006836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1101905</t>
+          <t>1105466</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1492817</t>
+          <t>1499170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1596405</t>
+          <t>1595396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2531178</t>
+          <t>2536395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2677487</t>
+          <t>2672696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1035421</t>
+          <t>1031860</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1130500</t>
+          <t>1130490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>913319</t>
+          <t>914328</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1016907</t>
+          <t>1010554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1969563</t>
+          <t>1974354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2115872</t>
+          <t>2110655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86488</t>
+          <t>85073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116902</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136730</t>
+          <t>136168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162567</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229099</t>
+          <t>230790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269527</t>
+          <t>273144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102247</t>
+          <t>103919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132661</t>
+          <t>134076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69989</t>
+          <t>70551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156341</t>
+          <t>152724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196769</t>
+          <t>195078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98014</t>
+          <t>98005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127810</t>
+          <t>129661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>157775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186112</t>
+          <t>187212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265793</t>
+          <t>265242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307772</t>
+          <t>305402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100953</t>
+          <t>99102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130749</t>
+          <t>130758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>56346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86017</t>
+          <t>85783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164549</t>
+          <t>166919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206528</t>
+          <t>207079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132613</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>169962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,82 +6704,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>51,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>58631</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47085</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>69998</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>47,85%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>38,43%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>210048</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>189758</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>233306</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>51,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58631</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48410</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>70991</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,85%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>57,94%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>210048</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>190506</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>232051</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>46,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160277</t>
+          <t>160516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197865</t>
+          <t>196016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,82 +6817,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>48,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>63897</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52530</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75443</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>52,15%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>42,87%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>61,57%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>242958</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>219700</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>263248</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>53,63%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>48,5%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63897</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51537</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74118</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>52,15%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>42,06%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>242958</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>220955</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>262500</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>53,63%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266390</t>
+          <t>268664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316341</t>
+          <t>316917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>302908</t>
+          <t>305253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>350328</t>
+          <t>348446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>581203</t>
+          <t>584833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>649718</t>
+          <t>651047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320480</t>
+          <t>319904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370431</t>
+          <t>368157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172246</t>
+          <t>174128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219666</t>
+          <t>217321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>509677</t>
+          <t>508348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578192</t>
+          <t>574562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>134302</t>
+          <t>135569</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172995</t>
+          <t>172904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238342</t>
+          <t>239860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286174</t>
+          <t>284983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>387920</t>
+          <t>391190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>450178</t>
+          <t>448800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202756</t>
+          <t>202847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241449</t>
+          <t>240182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213880</t>
+          <t>215071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261712</t>
+          <t>260194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425627</t>
+          <t>427005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>487885</t>
+          <t>484615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36791</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191308</t>
+          <t>191985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>241735</t>
+          <t>243758</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>218235</t>
+          <t>218723</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>271250</t>
+          <t>273408</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>68209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87586</t>
+          <t>87481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>487957</t>
+          <t>485934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>538384</t>
+          <t>537707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>563276</t>
+          <t>561118</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>616291</t>
+          <t>615803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>793044</t>
+          <t>796012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>881641</t>
+          <t>879129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1142699</t>
+          <t>1144883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1240786</t>
+          <t>1242090</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1960258</t>
+          <t>1958200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2095273</t>
+          <t>2092584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1014155</t>
+          <t>1016667</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1102752</t>
+          <t>1099784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1084339</t>
+          <t>1083035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1182426</t>
+          <t>1180242</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2125648</t>
+          <t>2128337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2260663</t>
+          <t>2262721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>25278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48106</t>
+          <t>48499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65313</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>71774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104017</t>
+          <t>104868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457106</t>
+          <t>456713</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480755</t>
+          <t>479934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>382154</t>
+          <t>383927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405891</t>
+          <t>405819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>848662</t>
+          <t>847811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881290</t>
+          <t>880905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17699</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>36765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57406</t>
+          <t>57699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>59444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89331</t>
+          <t>88420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414617</t>
+          <t>414199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434514</t>
+          <t>433601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325174</t>
+          <t>324881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347107</t>
+          <t>345815</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>745462</t>
+          <t>746373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775592</t>
+          <t>775349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76461</t>
+          <t>78027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92955</t>
+          <t>91806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>591803</t>
+          <t>590237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654141</t>
+          <t>650650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144155</t>
+          <t>142309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156201</t>
+          <t>155843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>742220</t>
+          <t>743369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810380</t>
+          <t>811634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86013</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127016</t>
+          <t>128144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115051</t>
+          <t>114349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>627293</t>
+          <t>567425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214710</t>
+          <t>218670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>852494</t>
+          <t>937526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907803</t>
+          <t>906675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>948806</t>
+          <t>948049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350801</t>
+          <t>410669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863043</t>
+          <t>863745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160418</t>
+          <t>1075386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1798202</t>
+          <t>1794242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50141</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76532</t>
+          <t>75344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124376</t>
+          <t>124621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113431</t>
+          <t>113867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164350</t>
+          <t>164480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>424545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448570</t>
+          <t>447845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716959</t>
+          <t>716714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>764803</t>
+          <t>765991</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1152031</t>
+          <t>1151901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1202950</t>
+          <t>1202514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80509</t>
+          <t>77401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112852</t>
+          <t>110881</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85989</t>
+          <t>85214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122842</t>
+          <t>123568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220786</t>
+          <t>219989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237145</t>
+          <t>237555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>648519</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>680862</t>
+          <t>683970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>879036</t>
+          <t>878310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>915889</t>
+          <t>916664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198912</t>
+          <t>204842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296680</t>
+          <t>299594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>415848</t>
+          <t>417253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1153448</t>
+          <t>1164698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>666224</t>
+          <t>667794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1485559</t>
+          <t>1514625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3079380</t>
+          <t>3076466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3177148</t>
+          <t>3171218</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2424310</t>
+          <t>2413060</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3161910</t>
+          <t>3160505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5468259</t>
+          <t>5439193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6287594</t>
+          <t>6286024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108945</t>
+          <t>109030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143390</t>
+          <t>144457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98026</t>
+          <t>96870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125846</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216249</t>
+          <t>213229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262390</t>
+          <t>259757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138378</t>
+          <t>137311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172823</t>
+          <t>172738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80505</t>
+          <t>80772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108325</t>
+          <t>109481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225729</t>
+          <t>228362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>271870</t>
+          <t>274890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79936</t>
+          <t>79757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111103</t>
+          <t>108499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131347</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159436</t>
+          <t>159358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219869</t>
+          <t>216633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260730</t>
+          <t>257969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>88019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116582</t>
+          <t>116761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64052</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>91733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159276</t>
+          <t>162037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200137</t>
+          <t>203373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116500</t>
+          <t>114499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150847</t>
+          <t>152414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59368</t>
+          <t>59721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82282</t>
+          <t>81782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181625</t>
+          <t>181445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225691</t>
+          <t>224450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188402</t>
+          <t>186835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222749</t>
+          <t>224750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66739</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239665</t>
+          <t>240906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283731</t>
+          <t>283911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>243145</t>
+          <t>239092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294418</t>
+          <t>291495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244615</t>
+          <t>244439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287352</t>
+          <t>286934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>497461</t>
+          <t>497339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564099</t>
+          <t>567235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482201</t>
+          <t>485124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533474</t>
+          <t>537527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182639</t>
+          <t>183057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>225376</t>
+          <t>225552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682511</t>
+          <t>679375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749149</t>
+          <t>749271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55984</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83095</t>
+          <t>83748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177166</t>
+          <t>177218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218599</t>
+          <t>216659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243841</t>
+          <t>242739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294026</t>
+          <t>293485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124104</t>
+          <t>123451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151215</t>
+          <t>150953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187132</t>
+          <t>189072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>228565</t>
+          <t>228513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>318905</t>
+          <t>319446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369090</t>
+          <t>370192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240561</t>
+          <t>237590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>293200</t>
+          <t>290896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>252819</t>
+          <t>255374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>309824</t>
+          <t>309393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97284</t>
+          <t>97291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>575421</t>
+          <t>577725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>628060</t>
+          <t>631031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>665640</t>
+          <t>666071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>722645</t>
+          <t>720090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>663650</t>
+          <t>662830</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>745626</t>
+          <t>751903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1012598</t>
+          <t>1011492</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1108999</t>
+          <t>1108073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1701223</t>
+          <t>1702672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1826901</t>
+          <t>1828361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1162570</t>
+          <t>1156293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1244546</t>
+          <t>1245366</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1191290</t>
+          <t>1192216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1287691</t>
+          <t>1288797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2381585</t>
+          <t>2380125</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2507263</t>
+          <t>2505814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145246</t>
+          <t>142379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178065</t>
+          <t>177610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151087</t>
+          <t>151669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176539</t>
+          <t>177177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>304302</t>
+          <t>306318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>345108</t>
+          <t>348796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77156</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109975</t>
+          <t>112842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55702</t>
+          <t>55120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116901</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157707</t>
+          <t>155691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141402</t>
+          <t>141838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177729</t>
+          <t>176807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185038</t>
+          <t>185681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209007</t>
+          <t>209901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>334342</t>
+          <t>336667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380889</t>
+          <t>382390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92554</t>
+          <t>93476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128881</t>
+          <t>128445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28153</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52122</t>
+          <t>51479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126554</t>
+          <t>125053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173101</t>
+          <t>170776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181046</t>
+          <t>181125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223247</t>
+          <t>221802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>95876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121377</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285940</t>
+          <t>286166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>336377</t>
+          <t>338691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185686</t>
+          <t>187131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227887</t>
+          <t>227808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61550</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86917</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255483</t>
+          <t>253169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>305920</t>
+          <t>305694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>341149</t>
+          <t>339181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395780</t>
+          <t>394969</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>384482</t>
+          <t>385711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>422799</t>
+          <t>425975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>736295</t>
+          <t>736463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>809740</t>
+          <t>808925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383938</t>
+          <t>384749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>438569</t>
+          <t>440537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>95728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137221</t>
+          <t>135992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>491681</t>
+          <t>492496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>565126</t>
+          <t>564958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>127939</t>
+          <t>129285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162768</t>
+          <t>164516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>338877</t>
+          <t>338327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385903</t>
+          <t>385574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>476419</t>
+          <t>478538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>539260</t>
+          <t>539254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157583</t>
+          <t>155835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192412</t>
+          <t>191066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200041</t>
+          <t>200370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247067</t>
+          <t>247617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367035</t>
+          <t>367041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>427757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>277298</t>
+          <t>278094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>333175</t>
+          <t>335390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>293543</t>
+          <t>294255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352619</t>
+          <t>351668</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76870</t>
+          <t>76858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92038</t>
+          <t>92456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>442026</t>
+          <t>439811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>497903</t>
+          <t>497107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525403</t>
+          <t>526354</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584479</t>
+          <t>583767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1006836</t>
+          <t>1010607</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1105466</t>
+          <t>1101968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1499170</t>
+          <t>1499081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1595396</t>
+          <t>1597490</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2536395</t>
+          <t>2529849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2672696</t>
+          <t>2670020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1031860</t>
+          <t>1035358</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1130490</t>
+          <t>1126719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>914328</t>
+          <t>912234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1010554</t>
+          <t>1010643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1974354</t>
+          <t>1977030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2110655</t>
+          <t>2117201</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85073</t>
+          <t>86288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115230</t>
+          <t>117345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136168</t>
+          <t>137389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162964</t>
+          <t>164572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230790</t>
+          <t>228257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273144</t>
+          <t>272303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,94%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103919</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>132861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43755</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152724</t>
+          <t>153565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195078</t>
+          <t>197611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98005</t>
+          <t>96920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129661</t>
+          <t>128008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157775</t>
+          <t>158370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187212</t>
+          <t>186631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265242</t>
+          <t>265434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305402</t>
+          <t>307954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99102</t>
+          <t>100755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130758</t>
+          <t>131843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85783</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166919</t>
+          <t>164367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207079</t>
+          <t>206887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134462</t>
+          <t>133633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169962</t>
+          <t>168575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>47641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69998</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189758</t>
+          <t>187906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233306</t>
+          <t>232484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160516</t>
+          <t>161903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196016</t>
+          <t>196845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52530</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75443</t>
+          <t>74887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219700</t>
+          <t>220522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263248</t>
+          <t>265100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>268664</t>
+          <t>264768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316917</t>
+          <t>316800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305253</t>
+          <t>305658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>348591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>584833</t>
+          <t>586953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>651047</t>
+          <t>652259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>319904</t>
+          <t>320021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368157</t>
+          <t>372053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174128</t>
+          <t>173983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>217321</t>
+          <t>216916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>508348</t>
+          <t>507136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574562</t>
+          <t>572442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135569</t>
+          <t>135021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172904</t>
+          <t>174205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239860</t>
+          <t>240970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>284983</t>
+          <t>289026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>391190</t>
+          <t>387420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448800</t>
+          <t>449682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202847</t>
+          <t>201546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>240182</t>
+          <t>240730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>215071</t>
+          <t>211028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260194</t>
+          <t>259084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>427005</t>
+          <t>426123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>484615</t>
+          <t>488385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36625</t>
+          <t>35626</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191985</t>
+          <t>193879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243758</t>
+          <t>244974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>218723</t>
+          <t>218172</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>273408</t>
+          <t>271868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68209</t>
+          <t>69208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87481</t>
+          <t>87281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>485934</t>
+          <t>484718</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>537707</t>
+          <t>535813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561118</t>
+          <t>562658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615803</t>
+          <t>616354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>796012</t>
+          <t>790834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>879129</t>
+          <t>881752</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1144883</t>
+          <t>1143067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1242090</t>
+          <t>1239616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1958200</t>
+          <t>1967124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2092584</t>
+          <t>2100307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1016667</t>
+          <t>1014044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1099784</t>
+          <t>1104962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1083035</t>
+          <t>1085509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1180242</t>
+          <t>1182058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2128337</t>
+          <t>2120614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2262721</t>
+          <t>2253797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,4%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25278</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48499</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51394</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41648</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63540</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>87031</t>
+          <t>97536</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71774</t>
+          <t>82137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104868</t>
+          <t>116286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>469575</t>
+          <t>510258</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456713</t>
+          <t>496099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479934</t>
+          <t>520447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>396073</t>
+          <t>431235</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383927</t>
+          <t>418942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405819</t>
+          <t>443048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>865648</t>
+          <t>941493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>847811</t>
+          <t>922743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>880905</t>
+          <t>956892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38014</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46319</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>41579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57699</t>
+          <t>66008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>83903</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59444</t>
+          <t>68807</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88420</t>
+          <t>100864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>425617</t>
+          <t>451771</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414199</t>
+          <t>438619</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433601</t>
+          <t>462017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>336261</t>
+          <t>370681</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324881</t>
+          <t>357135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345815</t>
+          <t>381564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>761878</t>
+          <t>822452</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>746373</t>
+          <t>805491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775349</t>
+          <t>837548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45134</t>
+          <t>52467</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>68885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>70507</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91806</t>
+          <t>88625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>623130</t>
+          <t>419145</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590237</t>
+          <t>402727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650650</t>
+          <t>431997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>150538</t>
+          <t>169457</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142309</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155843</t>
+          <t>175114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>773668</t>
+          <t>588602</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>743369</t>
+          <t>570484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811634</t>
+          <t>602450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>106257</t>
+          <t>126423</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86770</t>
+          <t>106570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128144</t>
+          <t>151434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>300658</t>
+          <t>110517</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114349</t>
+          <t>93812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>567425</t>
+          <t>129287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>406914</t>
+          <t>236939</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218670</t>
+          <t>209032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>937526</t>
+          <t>266452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>928562</t>
+          <t>1005420</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>906675</t>
+          <t>980409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>948049</t>
+          <t>1025273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677436</t>
+          <t>750694</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410669</t>
+          <t>731924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863745</t>
+          <t>767399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1605998</t>
+          <t>1756115</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1075386</t>
+          <t>1726602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1794242</t>
+          <t>1784022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>43921</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27201</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>58576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>102916</t>
+          <t>125400</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>109012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124621</t>
+          <t>144855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>140457</t>
+          <t>169321</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113867</t>
+          <t>147375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164480</t>
+          <t>191575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>437505</t>
+          <t>524043</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424545</t>
+          <t>509388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447845</t>
+          <t>535714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>738419</t>
+          <t>705450</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716714</t>
+          <t>685995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>765991</t>
+          <t>721838</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1175924</t>
+          <t>1229493</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1151901</t>
+          <t>1207239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1202514</t>
+          <t>1251439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>22879</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>109843</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77401</t>
+          <t>93935</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110881</t>
+          <t>132082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>102858</t>
+          <t>120353</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85214</t>
+          <t>100693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>141590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232008</t>
+          <t>226718</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219989</t>
+          <t>214349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237555</t>
+          <t>233558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>667012</t>
+          <t>734438</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>712199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>683970</t>
+          <t>750346</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>899020</t>
+          <t>961156</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>878310</t>
+          <t>939919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>916664</t>
+          <t>980816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>259663</t>
+          <t>305122</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204842</t>
+          <t>272039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>299594</t>
+          <t>342664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>612019</t>
+          <t>473438</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>417253</t>
+          <t>436908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1164698</t>
+          <t>510410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>871682</t>
+          <t>778560</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>667794</t>
+          <t>727792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1514625</t>
+          <t>830608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3116397</t>
+          <t>3137354</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3076466</t>
+          <t>3099812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3171218</t>
+          <t>3170437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2965739</t>
+          <t>3161955</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2413060</t>
+          <t>3124983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3160505</t>
+          <t>3198485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6082136</t>
+          <t>6299309</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5439193</t>
+          <t>6247261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6286024</t>
+          <t>6350077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
